--- a/remotes/keymapper/astrion/KeyCodes Astrion.xlsx
+++ b/remotes/keymapper/astrion/KeyCodes Astrion.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -841,33 +841,33 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F1 long-press</t>
+          <t>Channel Up long-press</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>131</v>
+        <v>92</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KEYCODE_F1</t>
+          <t>KEYCODE_PAGE_UP</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Android Go home</t>
+          <t>'</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>KEYCODE_APOSTROPHE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -879,33 +879,33 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F2 long-press</t>
+          <t>Channel Down long-press</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KEYCODE_F2</t>
+          <t>KEYCODE_PAGE_DOWN</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>76</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>KEYCODE_EQUALS</t>
+          <t>KEYCODE_SLASH</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -917,36 +917,112 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>F1 long-press</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>131</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>KEYCODE_F1</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>59</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Android Go home</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>group “FullyKiosk” — Fully Kiosk Browser in foreground</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>F2 long-press</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>132</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>KEYCODE_F2</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>60</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KEYCODE_EQUALS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>group “FullyKiosk” — Fully Kiosk Browser in foreground</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>F11 long-press</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B16" t="n">
         <v>141</v>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>KEYCODE_F11</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D16" t="n">
         <v>87</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Open Android Browser</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>com.android.browser</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>global</t>
         </is>

--- a/remotes/keymapper/astrion/KeyCodes Astrion.xlsx
+++ b/remotes/keymapper/astrion/KeyCodes Astrion.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -841,33 +841,33 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Channel Up long-press</t>
+          <t>D-pad Left long-press</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KEYCODE_PAGE_UP</t>
+          <t>KEYCODE_DPAD_LEFT</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>'</t>
+          <t>,</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>55</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>KEYCODE_APOSTROPHE</t>
+          <t>KEYCODE_COMMA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -879,33 +879,33 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Channel Down long-press</t>
+          <t>D-pad Right long-press</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KEYCODE_PAGE_DOWN</t>
+          <t>KEYCODE_DPAD_RIGHT</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>56</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>KEYCODE_SLASH</t>
+          <t>KEYCODE_PERIOD</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -917,33 +917,33 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F1 long-press</t>
+          <t>Channel Up long-press</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>131</v>
+        <v>92</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>KEYCODE_F1</t>
+          <t>KEYCODE_PAGE_UP</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Android Go home</t>
+          <t>'</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>KEYCODE_APOSTROPHE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -955,33 +955,33 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F2 long-press</t>
+          <t>Channel Down long-press</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KEYCODE_F2</t>
+          <t>KEYCODE_PAGE_DOWN</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>76</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>KEYCODE_EQUALS</t>
+          <t>KEYCODE_SLASH</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -993,36 +993,112 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>F1 long-press</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>131</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>KEYCODE_F1</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>59</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Android Go home</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>group “FullyKiosk” — Fully Kiosk Browser in foreground</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>F2 long-press</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>132</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>KEYCODE_F2</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>60</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KEYCODE_EQUALS</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>group “FullyKiosk” — Fully Kiosk Browser in foreground</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>F11 long-press</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B18" t="n">
         <v>141</v>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>KEYCODE_F11</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D18" t="n">
         <v>87</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Open Android Browser</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>com.android.browser</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>global</t>
         </is>

--- a/remotes/keymapper/astrion/KeyCodes Astrion.xlsx
+++ b/remotes/keymapper/astrion/KeyCodes Astrion.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Astrion" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw keys" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,7 +614,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F8 press</t>
+          <t>Red (F8) press</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -651,7 +652,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F9 press</t>
+          <t>Green (F9) press</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -689,7 +690,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F10 press</t>
+          <t>Blue (F10) press</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -727,7 +728,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F11 press</t>
+          <t>Yellow (F11) press</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -819,17 +820,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Android Go back</t>
+          <t>]</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>72</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>KEYCODE_RIGHT_BRACKET</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -917,33 +918,33 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Channel Up long-press</t>
+          <t>Menu long-press</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>KEYCODE_PAGE_UP</t>
+          <t>KEYCODE_MENU</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>'</t>
+          <t>@</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>77</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>KEYCODE_APOSTROPHE</t>
+          <t>KEYCODE_AT</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -955,33 +956,33 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Channel Down long-press</t>
+          <t>Channel Up long-press</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KEYCODE_PAGE_DOWN</t>
+          <t>KEYCODE_PAGE_UP</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>/</t>
+          <t>'</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>KEYCODE_SLASH</t>
+          <t>KEYCODE_APOSTROPHE</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -993,33 +994,33 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F1 long-press</t>
+          <t>Channel Down long-press</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>KEYCODE_F1</t>
+          <t>KEYCODE_PAGE_DOWN</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Android Go home</t>
+          <t>/</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>76</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>KEYCODE_SLASH</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1031,19 +1032,19 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F2 long-press</t>
+          <t>Home (F1) long-press</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>KEYCODE_F2</t>
+          <t>KEYCODE_F1</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1069,38 +1070,260 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F11 long-press</t>
+          <t>Power (F2) long-press</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>132</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>KEYCODE_F2</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>60</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KEYCODE_F12</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>group “FullyKiosk” — Fully Kiosk Browser in foreground</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Yellow (F11) long-press</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
         <v>141</v>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>KEYCODE_F11</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D19" t="n">
         <v>87</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Open Android Browser</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>com.android.browser</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>global</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Physical key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Emits</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>What Harmonium does</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>D-pad ▲ ▼ ◀ ▶</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Arrow keys</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>move panel focus · drive the device on TV pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>OK (center)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Enter</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>activate the focused card · hold = grab the D-pad</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Home (F1) tap</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Harmonium home — up one level</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Power (F2) tap</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>power — end/start the page's activity (confirm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Channel ▲/▼ tap</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PageUp / PageDown</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>jump sections · on TV pages: borrow the D-pad for the panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Lightbulb·REW (F4)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>astrion profile: Lights shortcut · astrion2: ⏮ previous</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Curtains·Play/Pause (F5)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>astrion: Covers shortcut · astrion2: ⏯</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Music·Stop (F6)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>F6</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>astrion: Music shortcut · astrion2: ⏹</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Climate·FWD (F7)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>astrion: Climate shortcut · astrion2: ⏭ next</t>
         </is>
       </c>
     </row>
